--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>-1.502952227589893</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>-4.469273743016744</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>-4.786923525977816</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>-2.302426882389552</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>0.8922443376801592</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>-5.660377358490565</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>-2.567661346287309</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>-2.127659574468077</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>-5.158184319119674</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>-2.451333813987022</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>-1.614086573734419</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>-2.415812591508049</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>-2.8592375366569</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>-2.718589272593674</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>-4.932735426008971</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>-1.089494163424121</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>-5.239520958083832</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>-1.433121019108274</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>-0.1619433198380538</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>-4.049844236760125</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>-1.940177849636204</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>-2.791461412151064</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>-2.721088435374153</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>-0.9532062391681029</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>-1.211072664359869</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>-0.5328596802841923</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>-1.496478873239437</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>-6.627516778523479</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>-3.157894736842115</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>-2.32766338406446</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>5.577299412915826</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1087,9 +989,6 @@
       <c r="E33">
         <v>0.19342359767891</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1109,9 +1008,6 @@
       <c r="E34">
         <v>-1.435406698564579</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1131,9 +1027,6 @@
       <c r="E35">
         <v>-1.274509803921564</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1153,9 +1046,6 @@
       <c r="E36">
         <v>-0.7042253521126751</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1175,9 +1065,6 @@
       <c r="E37">
         <v>-4.558680892337541</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1197,9 +1084,6 @@
       <c r="E38">
         <v>-1.208459214501501</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1219,9 +1103,6 @@
       <c r="E39">
         <v>-2.010050251256279</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1241,9 +1122,6 @@
       <c r="E40">
         <v>-0.6309148264984299</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1263,9 +1141,6 @@
       <c r="E41">
         <v>-6.442021803766107</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1285,9 +1160,6 @@
       <c r="E42">
         <v>-1.742919389978215</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1307,9 +1179,6 @@
       <c r="E43">
         <v>-0.4434589800443312</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1329,9 +1198,6 @@
       <c r="E44">
         <v>0.4519774011299438</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1351,9 +1217,6 @@
       <c r="E45">
         <v>-6.566200215285245</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1373,9 +1236,6 @@
       <c r="E46">
         <v>-3.033707865168533</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1395,9 +1255,6 @@
       <c r="E47">
         <v>1.914580265095722</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1417,9 +1274,6 @@
       <c r="E48">
         <v>-0.1457725947521915</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1439,9 +1293,6 @@
       <c r="E49">
         <v>0.9374999999999911</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1461,9 +1312,6 @@
       <c r="E50">
         <v>-2.348336594911937</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1483,9 +1331,6 @@
       <c r="E51">
         <v>0.7537688442210921</v>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1505,9 +1350,6 @@
       <c r="E52">
         <v>-1.262626262626254</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1526,9 +1368,6 @@
       </c>
       <c r="E53">
         <v>1.838235294117641</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1012,361 +1012,380 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B35">
-        <v>10.07</v>
+        <v>10.18</v>
       </c>
       <c r="C35">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D35">
-        <v>-0.129999999999999</v>
+        <v>-0.2200000000000006</v>
       </c>
       <c r="E35">
-        <v>-1.274509803921564</v>
+        <v>-2.115384615384619</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="B36">
-        <v>9.869999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="C36">
-        <v>9.94</v>
+        <v>10.2</v>
       </c>
       <c r="D36">
-        <v>-0.07000000000000028</v>
+        <v>-0.129999999999999</v>
       </c>
       <c r="E36">
-        <v>-0.7042253521126751</v>
+        <v>-1.274509803921564</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="B37">
-        <v>9.84</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C37">
-        <v>10.31</v>
+        <v>9.94</v>
       </c>
       <c r="D37">
-        <v>-0.4700000000000006</v>
+        <v>-0.07000000000000028</v>
       </c>
       <c r="E37">
-        <v>-4.558680892337541</v>
+        <v>-0.7042253521126751</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="B38">
-        <v>9.81</v>
+        <v>9.84</v>
       </c>
       <c r="C38">
-        <v>9.93</v>
+        <v>10.31</v>
       </c>
       <c r="D38">
-        <v>-0.1199999999999992</v>
+        <v>-0.4700000000000006</v>
       </c>
       <c r="E38">
-        <v>-1.208459214501501</v>
+        <v>-4.558680892337541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="B39">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="C39">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="D39">
-        <v>-0.1999999999999993</v>
+        <v>-0.1199999999999992</v>
       </c>
       <c r="E39">
-        <v>-2.010050251256279</v>
+        <v>-1.208459214501501</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="B40">
-        <v>9.449999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="C40">
-        <v>9.51</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D40">
-        <v>-0.0600000000000005</v>
+        <v>-0.1999999999999993</v>
       </c>
       <c r="E40">
-        <v>-0.6309148264984299</v>
+        <v>-2.010050251256279</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="B41">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C41">
-        <v>10.09</v>
+        <v>9.51</v>
       </c>
       <c r="D41">
-        <v>-0.6500000000000004</v>
+        <v>-0.0600000000000005</v>
       </c>
       <c r="E41">
-        <v>-6.442021803766107</v>
+        <v>-0.6309148264984299</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="B42">
-        <v>9.02</v>
+        <v>9.44</v>
       </c>
       <c r="C42">
-        <v>9.18</v>
+        <v>10.09</v>
       </c>
       <c r="D42">
-        <v>-0.1600000000000001</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="E42">
-        <v>-1.742919389978215</v>
+        <v>-6.442021803766107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="B43">
-        <v>8.98</v>
+        <v>9.02</v>
       </c>
       <c r="C43">
-        <v>9.02</v>
+        <v>9.18</v>
       </c>
       <c r="D43">
-        <v>-0.03999999999999915</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="E43">
-        <v>-0.4434589800443312</v>
+        <v>-1.742919389978215</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="B44">
-        <v>8.890000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="C44">
-        <v>8.85</v>
+        <v>9.02</v>
       </c>
       <c r="D44">
-        <v>0.04000000000000092</v>
+        <v>-0.03999999999999915</v>
       </c>
       <c r="E44">
-        <v>0.4519774011299438</v>
+        <v>-0.4434589800443312</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="B45">
-        <v>8.68</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C45">
-        <v>9.289999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="D45">
-        <v>-0.6099999999999994</v>
+        <v>0.04000000000000092</v>
       </c>
       <c r="E45">
-        <v>-6.566200215285245</v>
+        <v>0.4519774011299438</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="B46">
-        <v>8.630000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="C46">
-        <v>8.9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D46">
-        <v>-0.2699999999999996</v>
+        <v>-0.6099999999999994</v>
       </c>
       <c r="E46">
-        <v>-3.033707865168533</v>
+        <v>-6.566200215285245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="B47">
-        <v>6.92</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="C47">
-        <v>6.79</v>
+        <v>8.9</v>
       </c>
       <c r="D47">
-        <v>0.1299999999999999</v>
+        <v>-0.2699999999999996</v>
       </c>
       <c r="E47">
-        <v>1.914580265095722</v>
+        <v>-3.033707865168533</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="B48">
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
       <c r="C48">
-        <v>6.86</v>
+        <v>6.79</v>
       </c>
       <c r="D48">
-        <v>-0.01000000000000068</v>
+        <v>0.1299999999999999</v>
       </c>
       <c r="E48">
-        <v>-0.1457725947521915</v>
+        <v>1.914580265095722</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="B49">
-        <v>6.46</v>
+        <v>6.85</v>
       </c>
       <c r="C49">
-        <v>6.4</v>
+        <v>6.86</v>
       </c>
       <c r="D49">
-        <v>0.05999999999999961</v>
+        <v>-0.01000000000000068</v>
       </c>
       <c r="E49">
-        <v>0.9374999999999911</v>
+        <v>-0.1457725947521915</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="B50">
-        <v>4.99</v>
+        <v>6.46</v>
       </c>
       <c r="C50">
-        <v>5.11</v>
+        <v>6.4</v>
       </c>
       <c r="D50">
-        <v>-0.1200000000000001</v>
+        <v>0.05999999999999961</v>
       </c>
       <c r="E50">
-        <v>-2.348336594911937</v>
+        <v>0.9374999999999911</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="B51">
-        <v>4.01</v>
+        <v>4.99</v>
       </c>
       <c r="C51">
-        <v>3.98</v>
+        <v>5.11</v>
       </c>
       <c r="D51">
-        <v>0.0299999999999998</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="E51">
-        <v>0.7537688442210921</v>
+        <v>-2.348336594911937</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="B52">
-        <v>3.91</v>
+        <v>4.01</v>
       </c>
       <c r="C52">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="D52">
-        <v>-0.04999999999999982</v>
+        <v>0.0299999999999998</v>
       </c>
       <c r="E52">
-        <v>-1.262626262626254</v>
+        <v>0.7537688442210921</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>3.91</v>
+      </c>
+      <c r="C53">
+        <v>3.96</v>
+      </c>
+      <c r="D53">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="E53">
+        <v>-1.262626262626254</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Vitacura</t>
         </is>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>2.77</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <v>2.72</v>
       </c>
-      <c r="D53">
+      <c r="D54">
         <v>0.04999999999999982</v>
       </c>
-      <c r="E53">
+      <c r="E54">
         <v>1.838235294117641</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_metropolitana.xlsx
@@ -1396,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1405,530 +1405,369 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>18.35</v>
+          <t>San Joaquín</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>12.72</v>
+          <t>San Miguel</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>10.36</v>
+          <t>San Ramón</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>11.04</v>
+          <t>Independencia</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>14.04</v>
+          <t>La Cisterna</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>9.449999999999999</v>
+          <t>Peñalolén</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>12.33</v>
+          <t>Providencia</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>13.25</v>
+          <t>La Reina</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>13.53</v>
+          <t>Calera de Tango</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>12.66</v>
+          <t>Colina</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>11.2</v>
+          <t>Santiago</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>9.02</v>
+          <t>Lampa</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>11.43</v>
+          <t>Pirque</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>13.79</v>
+          <t>Puente Alto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>9.869999999999999</v>
+          <t>Huechuraba</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>10.07</v>
+          <t>San Bernardo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>13.24</v>
+          <t>Curacaví</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>15.7</v>
+          <t>María Pinto</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>6.92</v>
+          <t>Cerrillos</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>8.630000000000001</v>
+          <t>Cerro Navia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>4.01</v>
+          <t>Vitacura</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>6.46</v>
+          <t>Conchalí</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>13.33</v>
+          <t>El Bosque</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>13.41</v>
+          <t>Estación Central</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>8.98</v>
+          <t>La Florida</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>9.81</v>
+          <t>La Granja</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>14.7</v>
+          <t>La Pintana</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>17.1</v>
+          <t>Las Condes</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>4.99</v>
+          <t>Lo Barnechea</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>9.44</v>
+          <t>Lo Espejo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>16.31</v>
+          <t>Lo Prado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>12.32</v>
+          <t>Macul</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>10.3</v>
+          <t>Maipú</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>12.38</v>
+          <t>Ñuñoa</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>9.84</v>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>3.91</v>
+          <t>Pudahuel</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>11.19</v>
+          <t>Quilicura</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>11.42</v>
+          <t>Quinta Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>9.75</v>
+          <t>Recoleta</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>10.91</v>
+          <t>Renca</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>12.71</v>
+          <t>El Monte</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>12.13</v>
+          <t>Padre Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>11.84</v>
+          <t>Peñaflor</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>11.44</v>
+          <t>Talagante</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>10.79</v>
+          <t>Paine</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>6.85</v>
+          <t>Isla de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>14.5</v>
+          <t>Buin</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>13.8</v>
+          <t>San José de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>8.890000000000001</v>
+          <t>Tiltil</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>11.13</v>
+          <t>Melipilla</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tiltil</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>8.68</v>
+          <t>San Pedro</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>2.77</v>
+          <t>Alhué</t>
+        </is>
       </c>
     </row>
   </sheetData>
